--- a/volunteers.xlsx
+++ b/volunteers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gyt_system\zhiban_cloud_system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E906857-E8FE-4F58-B06C-1C130327D987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE3AECB-9E8A-4791-810D-A172B61748BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1453,9 +1453,6 @@
     <t>zhangguiling</t>
   </si>
   <si>
-    <t>张国齐</t>
-  </si>
-  <si>
     <t>0126342109</t>
   </si>
   <si>
@@ -1592,6 +1589,10 @@
   </si>
   <si>
     <t>01135899100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄国齐</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -4466,7 +4467,7 @@
         <v>20</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>271</v>
@@ -6320,16 +6321,16 @@
         <v>40</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>476</v>
+        <v>522</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D140" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>469</v>
@@ -6351,16 +6352,16 @@
         <v>108</v>
       </c>
       <c r="B141" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D141" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D141" s="2" t="s">
+      <c r="E141" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>469</v>
@@ -6382,16 +6383,16 @@
         <v>45</v>
       </c>
       <c r="B142" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D142" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D142" s="2" t="s">
+      <c r="E142" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>469</v>
@@ -6413,19 +6414,19 @@
         <v>147</v>
       </c>
       <c r="B143" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D143" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D143" s="2" t="s">
+      <c r="E143" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E143" s="2" t="s">
+      <c r="F143" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>16</v>
@@ -6444,16 +6445,16 @@
         <v>49</v>
       </c>
       <c r="B144" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D144" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="C144" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D144" s="2" t="s">
+      <c r="E144" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>469</v>
@@ -6475,16 +6476,16 @@
         <v>48</v>
       </c>
       <c r="B145" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D145" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="C145" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D145" s="2" t="s">
+      <c r="E145" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>469</v>
@@ -6506,16 +6507,16 @@
         <v>46</v>
       </c>
       <c r="B146" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D146" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="C146" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D146" s="2" t="s">
+      <c r="E146" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>469</v>
@@ -6537,7 +6538,7 @@
         <v>85</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>20</v>
@@ -6546,10 +6547,10 @@
         <v>404</v>
       </c>
       <c r="E147" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F147" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>16</v>
@@ -6568,19 +6569,19 @@
         <v>87</v>
       </c>
       <c r="B148" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D148" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C148" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D148" s="2" t="s">
+      <c r="E148" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="E148" s="2" t="s">
+      <c r="F148" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>16</v>
@@ -6599,19 +6600,19 @@
         <v>144</v>
       </c>
       <c r="B149" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D149" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D149" s="2" t="s">
+      <c r="E149" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="E149" s="2" t="s">
-        <v>507</v>
-      </c>
       <c r="F149" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>16</v>
@@ -6630,19 +6631,19 @@
         <v>104</v>
       </c>
       <c r="B150" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D150" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D150" s="2" t="s">
+      <c r="E150" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="E150" s="2" t="s">
+      <c r="F150" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>16</v>
@@ -6661,19 +6662,19 @@
         <v>30</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D151" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="F151" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>16</v>
@@ -6692,19 +6693,19 @@
         <v>84</v>
       </c>
       <c r="B152" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D152" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D152" s="2" t="s">
+      <c r="E152" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E152" s="2" t="s">
+      <c r="F152" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>16</v>
@@ -6723,7 +6724,7 @@
         <v>22</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>12</v>
@@ -6732,10 +6733,10 @@
         <v>46</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>16</v>
